--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.8649623615921</v>
+        <v>2.903056383758716</v>
       </c>
       <c r="D2" t="n">
-        <v>18.33792340617138</v>
+        <v>2.97991255350285</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04876082983263</v>
+        <v>2.770423634847802</v>
       </c>
       <c r="F2" t="n">
-        <v>16.77571442112217</v>
+        <v>2.726053593432353</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.95663388665104</v>
+        <v>3.892953006580794</v>
       </c>
       <c r="D3" t="n">
-        <v>24.49978758800846</v>
+        <v>3.981215483051376</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04876082983263</v>
+        <v>2.770423634847802</v>
       </c>
       <c r="F3" t="n">
-        <v>16.77571442112217</v>
+        <v>2.726053593432353</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.25391828006256</v>
+        <v>7.353761720510167</v>
       </c>
       <c r="D4" t="n">
-        <v>45.79688863407719</v>
+        <v>7.441994403037544</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04876082983263</v>
+        <v>2.770423634847802</v>
       </c>
       <c r="F4" t="n">
-        <v>16.77571442112217</v>
+        <v>2.726053593432353</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.93114953204728</v>
+        <v>8.926311798957682</v>
       </c>
       <c r="D5" t="n">
-        <v>53.67598308299316</v>
+        <v>8.72234725098639</v>
       </c>
       <c r="E5" t="n">
-        <v>17.04876082983263</v>
+        <v>2.770423634847802</v>
       </c>
       <c r="F5" t="n">
-        <v>16.77571442112217</v>
+        <v>2.726053593432353</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.944548752051107</v>
+        <v>1.128489172208305</v>
       </c>
       <c r="D6" t="n">
-        <v>6.689469508895237</v>
+        <v>1.087038795195476</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04876082983263</v>
+        <v>2.770423634847802</v>
       </c>
       <c r="F6" t="n">
-        <v>16.77571442112217</v>
+        <v>2.726053593432353</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.31535473643846</v>
+        <v>2.488745144671249</v>
       </c>
       <c r="D7" t="n">
-        <v>15.55852958637637</v>
+        <v>2.52826105778616</v>
       </c>
       <c r="E7" t="n">
-        <v>17.04876082983263</v>
+        <v>2.770423634847802</v>
       </c>
       <c r="F7" t="n">
-        <v>16.77571442112217</v>
+        <v>2.726053593432353</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
